--- a/data/price_raise_preview.xlsx
+++ b/data/price_raise_preview.xlsx
@@ -559,7 +559,7 @@
         <v>63</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>12890</v>
@@ -571,10 +571,10 @@
         <v>0.09309542280837868</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2227</v>
+        <v>2627</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2779</v>
+        <v>3179</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>9860</v>

--- a/data/price_raise_preview.xlsx
+++ b/data/price_raise_preview.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -85,6 +90,7 @@
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,7 +466,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -507,7 +513,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Рост %</t>
+          <t>Изменение %</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -565,19 +571,19 @@
         <v>12890</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>14090</v>
+        <v>13850</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.09309542280837868</v>
+        <v>0.07447633824670286</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>2627</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3179</v>
+        <v>3068</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>9860</v>
+        <v>9700</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -615,19 +621,19 @@
         <v>9850</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>10790</v>
+        <v>10850</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.09543147208121838</v>
+        <v>0.101522842639594</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>2566</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2999</v>
+        <v>3026</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>7550</v>
+        <v>7590</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -665,19 +671,19 @@
         <v>1479</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1590</v>
+        <v>1850</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.07505070993914797</v>
+        <v>0.2508451656524679</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>345</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>396</v>
+        <v>516</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1110</v>
+        <v>1300</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -686,7 +692,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.29): запас до конкурентов (ограничил +25%); ходовой (41 продаж) — не больше +10%</t>
+          <t>ходовой, но конкуренты от 3 174 — запас есть</t>
         </is>
       </c>
       <c r="N4" s="6" t="n"/>
@@ -715,19 +721,19 @@
         <v>4490</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4890</v>
+        <v>4850</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.08908685968819596</v>
+        <v>0.0801781737193763</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1030</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1214</v>
+        <v>1196</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3420</v>
+        <v>3400</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -765,19 +771,19 @@
         <v>6050</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6590</v>
+        <v>6350</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.08925619834710741</v>
+        <v>0.04958677685950419</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1684</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1932</v>
+        <v>1822</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4610</v>
+        <v>4450</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -815,19 +821,19 @@
         <v>3479</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3790</v>
+        <v>3850</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.08939350388042544</v>
+        <v>0.1066398390342052</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1215</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1358</v>
+        <v>1386</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -865,19 +871,19 @@
         <v>1610</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.04968944099378891</v>
+        <v>0.1490683229813665</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>476</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>512</v>
+        <v>586</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -915,19 +921,19 @@
         <v>879</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1090</v>
+        <v>950</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.2400455062571103</v>
+        <v>0.08077360637087594</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>174</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>760</v>
+        <v>670</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -965,19 +971,19 @@
         <v>4490</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4890</v>
+        <v>4850</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.08908685968819596</v>
+        <v>0.0801781737193763</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1130</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3420</v>
+        <v>3400</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1015,19 +1021,19 @@
         <v>1240</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1290</v>
+        <v>1350</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.04032258064516125</v>
+        <v>0.08870967741935476</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>395</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1065,19 +1071,19 @@
         <v>3879</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4390</v>
+        <v>4350</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.1317349832431038</v>
+        <v>0.1214230471771076</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1249</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1484</v>
+        <v>1466</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>3070</v>
+        <v>3050</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1115,19 +1121,19 @@
         <v>1990</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2090</v>
+        <v>2350</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.05025125628140703</v>
+        <v>0.1809045226130652</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>680</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>726</v>
+        <v>846</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1460</v>
+        <v>1650</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1165,19 +1171,19 @@
         <v>1490</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1590</v>
+        <v>1850</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.06711409395973145</v>
+        <v>0.2416107382550337</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>300</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>346</v>
+        <v>466</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1110</v>
+        <v>1300</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1215,19 +1221,19 @@
         <v>2890</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3090</v>
+        <v>3350</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.0692041522491349</v>
+        <v>0.1591695501730104</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>794</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>886</v>
+        <v>1006</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2160</v>
+        <v>2350</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -1265,19 +1271,19 @@
         <v>68800</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>75090</v>
+        <v>74850</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.09142441860465111</v>
+        <v>0.0879360465116279</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>15972</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>18866</v>
+        <v>18756</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>45050</v>
+        <v>44910</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -1315,19 +1321,19 @@
         <v>8879</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>9690</v>
+        <v>9850</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.09133911476517631</v>
+        <v>0.1093591620678005</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>3177</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3550</v>
+        <v>3624</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>6780</v>
+        <v>6900</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1365,19 +1371,19 @@
         <v>1880</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1990</v>
+        <v>2350</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.0585106382978724</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>630</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>680</v>
+        <v>846</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1390</v>
+        <v>1650</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1415,19 +1421,19 @@
         <v>3879</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4190</v>
+        <v>4350</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.08017530291312203</v>
+        <v>0.1214230471771076</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1449</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1592</v>
+        <v>1666</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2930</v>
+        <v>3050</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -1465,19 +1471,19 @@
         <v>2879</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3590</v>
+        <v>3350</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.2469607502605071</v>
+        <v>0.1635984716915595</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>673</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2510</v>
+        <v>2350</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1515,19 +1521,19 @@
         <v>4130</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4490</v>
+        <v>4350</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.0871670702179177</v>
+        <v>0.0532687651331718</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1249</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1414</v>
+        <v>1350</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3140</v>
+        <v>3050</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -1565,19 +1571,19 @@
         <v>1240</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.2016129032258065</v>
+        <v>0.08870967741935476</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>405</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>520</v>
+        <v>456</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -1615,19 +1621,19 @@
         <v>9479</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10390</v>
+        <v>10850</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.09610718430214149</v>
+        <v>0.1446355100749024</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>2825</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3244</v>
+        <v>3456</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7270</v>
+        <v>7590</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -1665,19 +1671,19 @@
         <v>3620</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4090</v>
+        <v>3850</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.1298342541436464</v>
+        <v>0.06353591160220984</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1130</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1346</v>
+        <v>1236</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2860</v>
+        <v>2700</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -1715,19 +1721,19 @@
         <v>1950</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2190</v>
+        <v>2350</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.1230769230769231</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>396</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1530</v>
+        <v>1650</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -1765,19 +1771,19 @@
         <v>931</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.06337271750805584</v>
+        <v>0.02040816326530615</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>143</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -1815,19 +1821,19 @@
         <v>128800</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>141590</v>
+        <v>141850</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.09930124223602488</v>
+        <v>0.1013198757763976</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>27590</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>33474</v>
+        <v>33594</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>84950</v>
+        <v>85110</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -1865,19 +1871,19 @@
         <v>8850</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9690</v>
+        <v>9850</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.09491525423728819</v>
+        <v>0.1129943502824859</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2920</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3306</v>
+        <v>3380</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>6780</v>
+        <v>6900</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -1915,19 +1921,19 @@
         <v>2879</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3090</v>
+        <v>3350</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.07328933657519965</v>
+        <v>0.1635984716915595</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>923</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1020</v>
+        <v>1140</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2160</v>
+        <v>2350</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -1965,19 +1971,19 @@
         <v>2366</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2590</v>
+        <v>2850</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.09467455621301779</v>
+        <v>0.2045646661031277</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>787</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>890</v>
+        <v>1010</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1810</v>
+        <v>1990</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -1994,40 +2000,40 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>90</v>
+        <v>280</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1620</v>
+        <v>1690</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.04320987654320985</v>
+        <v>0.09467455621301779</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>520</v>
+        <v>333</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>552</v>
+        <v>406</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2036,7 +2042,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N31" s="6" t="n"/>
@@ -2044,40 +2050,40 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1479</v>
+        <v>1620</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1590</v>
+        <v>1850</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.07505070993914797</v>
+        <v>0.1419753086419753</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>445</v>
+        <v>520</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>496</v>
+        <v>626</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1110</v>
+        <v>1300</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -2094,49 +2100,49 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18000</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>78800</v>
+        <v>1479</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>85990</v>
+        <v>1850</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.09124365482233499</v>
+        <v>0.2508451656524679</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>17690</v>
+        <v>445</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>20997</v>
+        <v>616</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>51590</v>
+        <v>1300</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N33" s="6" t="n"/>
@@ -2144,49 +2150,49 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>19800</v>
+        <v>78800</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22690</v>
+        <v>85850</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.1459595959595961</v>
+        <v>0.08946700507614214</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1944</v>
+        <v>17690</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3273</v>
+        <v>20932</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>15880</v>
+        <v>51510</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
         </is>
       </c>
       <c r="N34" s="6" t="n"/>
@@ -2194,40 +2200,40 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>600</v>
+        <v>7000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4990</v>
+        <v>19800</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5390</v>
+        <v>22850</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.08016032064128265</v>
+        <v>0.154040404040404</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1560</v>
+        <v>1944</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1744</v>
+        <v>3346</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3770</v>
+        <v>15990</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -2236,7 +2242,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N35" s="6" t="n"/>
@@ -2244,40 +2250,40 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2980</v>
+        <v>4990</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>3190</v>
+        <v>5350</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.07046979865771807</v>
+        <v>0.07214428857715438</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1086</v>
+        <v>1560</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1182</v>
+        <v>1726</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2230</v>
+        <v>3740</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -2294,16 +2300,16 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>4</v>
@@ -2312,22 +2318,22 @@
         <v>150</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2860</v>
+        <v>2980</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>3090</v>
+        <v>3350</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.08041958041958042</v>
+        <v>0.1241610738255035</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1001</v>
+        <v>1086</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1107</v>
+        <v>1256</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>2160</v>
+        <v>2350</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -2344,40 +2350,40 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2490</v>
+        <v>2860</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2690</v>
+        <v>3350</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.08032128514056236</v>
+        <v>0.1713286713286712</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>910</v>
+        <v>1001</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1002</v>
+        <v>1226</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1880</v>
+        <v>2350</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -2394,40 +2400,40 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>980</v>
+        <v>2490</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1090</v>
+        <v>2850</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.1122448979591837</v>
+        <v>0.1445783132530121</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>166</v>
+        <v>910</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>216</v>
+        <v>1076</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>760</v>
+        <v>1990</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N39" s="6" t="n"/>
@@ -2444,40 +2450,40 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6690</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>7290</v>
+        <v>980</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>950</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.08968609865470856</v>
+        <v>-0.03061224489795922</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2226</v>
+        <v>166</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2502</v>
+        <v>152</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>5100</v>
+        <v>670</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -2486,7 +2492,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>ближайшая красивая цена</t>
         </is>
       </c>
       <c r="N40" s="6" t="n"/>
@@ -2494,40 +2500,40 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
+          <t>Комплект: алюминиевый корпус (крышка) масляного фильтра + обратный клапан EA888 Gen3 06L115401S 06L115678AD</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>4741</v>
+        <v>6690</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>5190</v>
+        <v>7350</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.0947057582788442</v>
+        <v>0.09865470852017943</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1410</v>
+        <v>2226</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1616</v>
+        <v>2530</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3630</v>
+        <v>5150</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -2544,49 +2550,49 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>40000</v>
+        <v>600</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>118000</v>
+        <v>4741</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>128790</v>
+        <v>5350</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.09144067796610167</v>
+        <v>0.1284539126766504</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13622</v>
+        <v>1410</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>18586</v>
+        <v>1690</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>77270</v>
+        <v>3740</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N42" s="6" t="n"/>
@@ -2594,40 +2600,40 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>78475</v>
+        <v>118000</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>85690</v>
+        <v>128850</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.09194010831474997</v>
+        <v>0.09194915254237279</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>18423</v>
+        <v>13622</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21742</v>
+        <v>18614</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>51410</v>
+        <v>77310</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -2644,49 +2650,49 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>900</v>
+        <v>15000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>8890</v>
+        <v>78475</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>9690</v>
+        <v>85850</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.08998875140607421</v>
+        <v>0.09397897419560364</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>3025</v>
+        <v>18423</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3393</v>
+        <v>21816</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>6780</v>
+        <v>51510</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
         </is>
       </c>
       <c r="N44" s="6" t="n"/>
@@ -2694,42 +2700,40 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>7500</v>
+        <v>8890</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>8690</v>
+        <v>9850</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.1586666666666667</v>
+        <v>0.1079865016872892</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1243</v>
+        <v>3025</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1790</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>фикс</t>
-        </is>
+        <v>3466</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>6900</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -2738,7 +2742,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>плита+фильтр; плита отдельно 6 990. На Авито у него ручная цена 5 850 (фикс) — предлагаю снять фикс</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N45" s="6" t="n"/>
@@ -2746,49 +2750,51 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3850</v>
+        <v>7500</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4790</v>
+        <v>8850</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.2441558441558442</v>
+        <v>0.1799999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1136</v>
+        <v>1243</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>1568</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>3350</v>
+        <v>1864</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>фикс 5 850</t>
+        </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.74): запас до конкурентов (ограничил +25%)</t>
+          <t>плита+фильтр. На Авито ручная цена 5 850 (фикс) — предлагаю снять фикс</t>
         </is>
       </c>
       <c r="N46" s="6" t="n"/>
@@ -2796,40 +2802,40 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>999</v>
+        <v>3850</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1190</v>
+        <v>4850</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.1911911911911912</v>
+        <v>0.2597402597402598</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>265</v>
+        <v>1136</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>352</v>
+        <v>1596</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>830</v>
+        <v>3400</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -2838,7 +2844,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.24): запас до конкурентов (ограничил +25%)</t>
+          <t>индекс зелёный (0.74): запас до конкурентов (ограничил +25%)</t>
         </is>
       </c>
       <c r="N47" s="6" t="n"/>
@@ -2846,40 +2852,40 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>979</v>
+        <v>999</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1190</v>
+        <v>1350</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.2155260469867211</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>830</v>
+        <v>940</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -2896,40 +2902,40 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>8900</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>9790</v>
+        <v>990</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>950</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.1000000000000001</v>
+        <v>-0.04040404040404044</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2959</v>
+        <v>220</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>3368</v>
+        <v>202</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>6850</v>
+        <v>670</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -2938,7 +2944,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N49" s="6" t="n"/>
@@ -2946,49 +2952,49 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2100</v>
+        <v>20</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>8500</v>
+        <v>979</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>10290</v>
+        <v>1350</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.2105882352941177</v>
+        <v>0.3789581205311543</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1603</v>
+        <v>295</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2426</v>
+        <v>466</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>7200</v>
+        <v>940</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>ориг. сальники: +500</t>
+          <t>индекс зелёный (0.24): запас до конкурентов (ограничил +25%)</t>
         </is>
       </c>
       <c r="N50" s="6" t="n"/>
@@ -2996,12 +3002,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3011,25 +3017,25 @@
         <v>1</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>7400</v>
+        <v>8900</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>8090</v>
+        <v>9850</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.09324324324324329</v>
+        <v>0.1067415730337078</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1969</v>
+        <v>2959</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2286</v>
+        <v>3396</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>5660</v>
+        <v>6900</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -3046,49 +3052,49 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>500</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2890</v>
+        <v>8500</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>2990</v>
+        <v>10850</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.03460207612456756</v>
+        <v>0.276470588235294</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>665</v>
+        <v>1603</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>711</v>
+        <v>2684</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>2090</v>
+        <v>7590</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.90): запас до конкурентов</t>
+          <t>ориг. сальники</t>
         </is>
       </c>
       <c r="N52" s="6" t="n"/>
@@ -3096,40 +3102,40 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2350</v>
+        <v>7400</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2490</v>
+        <v>7850</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.05957446808510647</v>
+        <v>0.06081081081081074</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>746</v>
+        <v>1969</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>810</v>
+        <v>2176</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1740</v>
+        <v>5500</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -3146,49 +3152,49 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>180</v>
+        <v>1900</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1990</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>2090</v>
+        <v>6990</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>6850</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.05025125628140703</v>
+        <v>-0.02002861230329045</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>600</v>
+        <v>1108</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>646</v>
+        <v>1044</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>1460</v>
+        <v>4800</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N54" s="6" t="n"/>
@@ -3196,49 +3202,49 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>999</v>
+        <v>2890</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1090</v>
+        <v>3350</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.09109109109109115</v>
+        <v>0.1591695501730104</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>255</v>
+        <v>665</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>296</v>
+        <v>876</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>760</v>
+        <v>2350</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>индекс зелёный (0.90): запас до конкурентов</t>
         </is>
       </c>
       <c r="N55" s="6" t="n"/>
@@ -3246,40 +3252,40 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>850</v>
+        <v>2350</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>890</v>
+        <v>2850</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.04705882352941182</v>
+        <v>0.2127659574468086</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>226</v>
+        <v>746</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>244</v>
+        <v>976</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>620</v>
+        <v>1990</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -3296,40 +3302,40 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>840</v>
+        <v>1990</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>890</v>
+        <v>2350</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.1809045226130652</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>201</v>
+        <v>600</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>224</v>
+        <v>766</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>620</v>
+        <v>1650</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3344,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N57" s="6" t="n"/>
@@ -3346,40 +3352,40 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>10000</v>
+        <v>70</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>58900</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>64790</v>
+        <v>999</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>950</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.1000000000000001</v>
+        <v>-0.04904904904904905</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>15570</v>
+        <v>255</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>18279</v>
+        <v>232</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>38870</v>
+        <v>670</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -3388,7 +3394,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%; дорогой — не больше +10%</t>
+          <t>ближайшая красивая цена</t>
         </is>
       </c>
       <c r="N58" s="6" t="n"/>
@@ -3396,40 +3402,40 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>58900</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>64790</v>
+        <v>990</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>950</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.1000000000000001</v>
+        <v>-0.04040404040404044</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>15570</v>
+        <v>240</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>18279</v>
+        <v>222</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>38870</v>
+        <v>670</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -3438,7 +3444,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%; дорогой — не больше +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N59" s="6" t="n"/>
@@ -3446,49 +3452,49 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>58900</v>
+        <v>850</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>64290</v>
+        <v>950</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.09151103565365015</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>15570</v>
+        <v>226</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>18049</v>
+        <v>272</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>38570</v>
+        <v>670</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N60" s="6" t="n"/>
@@ -3496,40 +3502,40 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2500</v>
+        <v>50</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>16890</v>
+        <v>840</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>18490</v>
+        <v>950</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.09473060982830073</v>
+        <v>0.1309523809523809</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>5098</v>
+        <v>201</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>5834</v>
+        <v>252</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>12940</v>
+        <v>670</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -3538,7 +3544,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N61" s="6" t="n"/>
@@ -3546,12 +3552,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -3561,25 +3567,25 @@
         <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>12979</v>
+        <v>58900</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>14190</v>
+        <v>64850</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.09330456891902306</v>
+        <v>0.1010186757215619</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>4335</v>
+        <v>15570</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>4892</v>
+        <v>18307</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>9930</v>
+        <v>38910</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -3588,7 +3594,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>конкурентов Ozon не видит: +10%; дорогой — не больше +10%</t>
         </is>
       </c>
       <c r="N62" s="6" t="n"/>
@@ -3596,12 +3602,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -3611,25 +3617,25 @@
         <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>11979</v>
+        <v>58900</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>13690</v>
+        <v>64850</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.1428332915936221</v>
+        <v>0.1010186757215619</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>2346</v>
+        <v>15570</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>3133</v>
+        <v>18307</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>9580</v>
+        <v>38910</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -3638,7 +3644,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>конкурентов Ozon не видит: +10%; дорогой — не больше +10%</t>
         </is>
       </c>
       <c r="N63" s="6" t="n"/>
@@ -3646,49 +3652,49 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>11979</v>
+        <v>58900</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>13090</v>
+        <v>63850</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.09274563820018367</v>
+        <v>0.08404074702886244</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>3546</v>
+        <v>15570</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>4057</v>
+        <v>17847</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>9160</v>
+        <v>38310</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>индекс зелёный (0.87): запас до конкурентов; дорогой — не больше +10%</t>
         </is>
       </c>
       <c r="N64" s="6" t="n"/>
@@ -3696,40 +3702,40 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>9500</v>
+        <v>16890</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>10990</v>
+        <v>18850</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.1568421052631579</v>
+        <v>0.1160449970396684</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>2063</v>
+        <v>5098</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>2748</v>
+        <v>6000</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>7690</v>
+        <v>13200</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -3738,7 +3744,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>полный комплект</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N65" s="6" t="n"/>
@@ -3746,12 +3752,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -3761,34 +3767,34 @@
         <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>9500</v>
+        <v>12979</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>11490</v>
+        <v>13850</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.2094736842105263</v>
+        <v>0.06710840588643197</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1963</v>
+        <v>4335</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2878</v>
+        <v>4736</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>8040</v>
+        <v>9700</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>полный комплект ориг.: +500</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N66" s="6" t="n"/>
@@ -3796,12 +3802,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -3811,34 +3817,34 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>9500</v>
+        <v>11979</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>10290</v>
+        <v>13850</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.0831578947368421</v>
+        <v>0.1561899991652058</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2063</v>
+        <v>2346</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>2426</v>
+        <v>3206</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>7200</v>
+        <v>9700</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>ориг.: +500</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N67" s="6" t="n"/>
@@ -3846,12 +3852,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -3861,34 +3867,34 @@
         <v>0</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>9500</v>
+        <v>11979</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>10290</v>
+        <v>12850</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.0831578947368421</v>
+        <v>0.07271057684280824</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2063</v>
+        <v>3546</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>2426</v>
+        <v>3946</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>дубль -orig: одна цена</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N68" s="6" t="n"/>
@@ -3896,40 +3902,40 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>8979</v>
+        <v>9500</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>9790</v>
+        <v>10850</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.09032186212273086</v>
+        <v>0.1421052631578947</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>2595</v>
+        <v>2063</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>2968</v>
+        <v>2684</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>6850</v>
+        <v>7590</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -3938,7 +3944,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>полный комплект</t>
         </is>
       </c>
       <c r="N69" s="6" t="n"/>
@@ -3946,49 +3952,49 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>8890</v>
+        <v>9500</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>10190</v>
+        <v>11850</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.1462317210348707</v>
+        <v>0.2473684210526317</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2125</v>
+        <v>1963</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2723</v>
+        <v>3044</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>7130</v>
+        <v>8300</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>полный комплект ориг.</t>
         </is>
       </c>
       <c r="N70" s="6" t="n"/>
@@ -3996,49 +4002,49 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>9790</v>
+        <v>10850</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.151764705882353</v>
+        <v>0.1421052631578947</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>1703</v>
+        <v>2063</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2296</v>
+        <v>2684</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>6850</v>
+        <v>7590</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>плита+фильтр+2 пыльника</t>
+          <t>ориг.</t>
         </is>
       </c>
       <c r="N71" s="6" t="n"/>
@@ -4046,12 +4052,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4064,31 +4070,31 @@
         <v>2100</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>10290</v>
+        <v>10850</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.2105882352941177</v>
+        <v>0.1421052631578947</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1603</v>
+        <v>2063</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2426</v>
+        <v>2684</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>7200</v>
+        <v>7590</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>ориг. пыльники: +500</t>
+          <t>дубль -orig</t>
         </is>
       </c>
       <c r="N72" s="6" t="n"/>
@@ -4096,49 +4102,49 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>8500</v>
+        <v>8979</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>9790</v>
+        <v>9850</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.151764705882353</v>
+        <v>0.09700412072613873</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1803</v>
+        <v>2595</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2396</v>
+        <v>2996</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>6850</v>
+        <v>6900</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>наравне с плита+фильтр+пыльники</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N73" s="6" t="n"/>
@@ -4146,40 +4152,40 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>7979</v>
+        <v>8890</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>8690</v>
+        <v>9850</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.08910891089108919</v>
+        <v>0.1079865016872892</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2519</v>
+        <v>2125</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2846</v>
+        <v>2566</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>6080</v>
+        <v>6900</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
@@ -4188,7 +4194,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N74" s="6" t="n"/>
@@ -4196,12 +4202,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -4214,31 +4220,31 @@
         <v>2000</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>8690</v>
+        <v>9850</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.1586666666666667</v>
+        <v>0.1588235294117648</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1243</v>
+        <v>1703</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1790</v>
+        <v>2324</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>6080</v>
+        <v>6900</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>дубль plita-filtr-v2 — одна цена</t>
+          <t>плита+фильтр+2 пыльника</t>
         </is>
       </c>
       <c r="N75" s="6" t="n"/>
@@ -4246,16 +4252,16 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0</v>
@@ -4264,22 +4270,22 @@
         <v>2100</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>9190</v>
+        <v>10850</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.2253333333333334</v>
+        <v>0.276470588235294</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1143</v>
+        <v>1603</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1920</v>
+        <v>2684</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>6430</v>
+        <v>7590</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -4288,7 +4294,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>улучшенный фильтр: +500 к обычному</t>
+          <t>ориг. пыльники — дороже обычных</t>
         </is>
       </c>
       <c r="N76" s="6" t="n"/>
@@ -4296,40 +4302,40 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>400</v>
+        <v>1900</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3990</v>
+        <v>8500</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>4390</v>
+        <v>9850</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.100250626566416</v>
+        <v>0.1588235294117648</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>1300</v>
+        <v>1803</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>1484</v>
+        <v>2424</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>3070</v>
+        <v>6900</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -4338,7 +4344,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>нет на Ozon; +10%</t>
+          <t>плита+2 пыльника+2 сальника</t>
         </is>
       </c>
       <c r="N77" s="6" t="n"/>
@@ -4346,49 +4352,49 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>3990</v>
+        <v>7979</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>4390</v>
+        <v>8850</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.100250626566416</v>
+        <v>0.1091615490662989</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1300</v>
+        <v>2519</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1484</v>
+        <v>2920</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>3070</v>
+        <v>6200</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>дубль: одна цена</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N78" s="6" t="n"/>
@@ -4396,43 +4402,49 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="3" t="n"/>
+      <c r="E79" s="3" t="n">
+        <v>2000</v>
+      </c>
       <c r="F79" s="3" t="n">
-        <v>3879</v>
+        <v>7500</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>4790</v>
+        <v>8850</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.2348543439030677</v>
-      </c>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>1243</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>1864</v>
+      </c>
       <c r="K79" s="3" t="n">
-        <v>3350</v>
+        <v>6200</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.23): запас до конкурентов (ограничил +25%)</t>
+          <t>плита+фильтр; дубль plita-filtr-v2 — одна цена</t>
         </is>
       </c>
       <c r="N79" s="6" t="n"/>
@@ -4440,40 +4452,40 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>150</v>
+        <v>2100</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2980</v>
+        <v>7500</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>3190</v>
+        <v>9350</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.07046979865771807</v>
+        <v>0.2466666666666666</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1086</v>
+        <v>1143</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>1182</v>
+        <v>1994</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>2230</v>
+        <v>6550</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -4482,7 +4494,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>улучшенный фильтр — дороже обычного</t>
         </is>
       </c>
       <c r="N80" s="6" t="n"/>
@@ -4490,40 +4502,40 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2850</v>
+        <v>3990</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4690</v>
+        <v>4350</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.6456140350877193</v>
+        <v>0.09022556390977443</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>676</v>
+        <v>1300</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>1522</v>
+        <v>1466</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>3280</v>
+        <v>3050</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -4532,7 +4544,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>ориг. дороже неоригинального 0am325025G</t>
+          <t>нет на Ozon; +10%</t>
         </is>
       </c>
       <c r="N81" s="6" t="n"/>
@@ -4540,40 +4552,40 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2850</v>
+        <v>3990</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4690</v>
+        <v>4350</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.6456140350877193</v>
+        <v>0.09022556390977443</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>676</v>
+        <v>1300</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>1522</v>
+        <v>1466</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>3280</v>
+        <v>3050</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -4590,49 +4602,43 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n">
-        <v>2450</v>
+        <v>3879</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>2690</v>
+        <v>4850</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.09795918367346945</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>958</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>1068</v>
-      </c>
+        <v>0.2503222480020624</v>
+      </c>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="n">
-        <v>1880</v>
+        <v>3400</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>индекс зелёный (0.23): запас до конкурентов (ограничил +25%)</t>
         </is>
       </c>
       <c r="N83" s="6" t="n"/>
@@ -4640,40 +4646,40 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1950</v>
+        <v>2980</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>2090</v>
+        <v>3350</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.07179487179487176</v>
+        <v>0.1241610738255035</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>562</v>
+        <v>1086</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>626</v>
+        <v>1256</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>1460</v>
+        <v>2350</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -4690,49 +4696,49 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1890</v>
+        <v>2850</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>1990</v>
+        <v>4850</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.05291005291005302</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>484</v>
+        <v>676</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>530</v>
+        <v>1596</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1390</v>
+        <v>3400</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>ориг. должен быть дороже неоригинального (4 350); остаток 0</t>
         </is>
       </c>
       <c r="N85" s="6" t="n"/>
@@ -4740,49 +4746,49 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1690</v>
+        <v>2850</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1790</v>
+        <v>4850</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0.05917159763313617</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>592</v>
+        <v>676</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>638</v>
+        <v>1596</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1250</v>
+        <v>3400</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>дубль: одна цена</t>
         </is>
       </c>
       <c r="N86" s="6" t="n"/>
@@ -4790,40 +4796,40 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1490</v>
+        <v>2790</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1590</v>
+        <v>2850</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0.06711409395973145</v>
+        <v>0.021505376344086</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>1110</v>
+        <v>1990</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -4832,7 +4838,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N87" s="6" t="n"/>
@@ -4840,49 +4846,49 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1490</v>
+        <v>2450</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1590</v>
+        <v>2850</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.06711409395973145</v>
+        <v>0.1632653061224489</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>430</v>
+        <v>958</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>476</v>
+        <v>1142</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>1110</v>
+        <v>1990</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>тот же товар, что 0сц</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N88" s="6" t="n"/>
@@ -4890,40 +4896,36 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1490</v>
+        <v>2290</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>1590</v>
+        <v>2350</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.06711409395973145</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>430</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>476</v>
-      </c>
+        <v>0.02620087336244548</v>
+      </c>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="n">
-        <v>1110</v>
+        <v>1650</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -4932,7 +4934,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>тот же товар, что 0сц</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N89" s="6" t="n"/>
@@ -4940,40 +4942,40 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1380</v>
+        <v>1950</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1490</v>
+        <v>2350</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.07971014492753614</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>350</v>
+        <v>562</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>400</v>
+        <v>746</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>1040</v>
+        <v>1650</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -4990,40 +4992,40 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1290</v>
+        <v>1890</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>1390</v>
+        <v>2350</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.07751937984496116</v>
+        <v>0.2433862433862435</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>258</v>
+        <v>484</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>304</v>
+        <v>696</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>970</v>
+        <v>1650</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -5032,7 +5034,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N91" s="6" t="n"/>
@@ -5040,40 +5042,40 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>950</v>
+        <v>1690</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>990</v>
+        <v>1850</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.04210526315789465</v>
+        <v>0.09467455621301779</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>295</v>
+        <v>500</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>690</v>
+        <v>1300</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -5082,7 +5084,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N92" s="6" t="n"/>
@@ -5090,45 +5092,49 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>580</v>
+        <v>1690</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>690</v>
+        <v>1850</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.1896551724137931</v>
-      </c>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
+        <v>0.09467455621301779</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>666</v>
+      </c>
       <c r="K93" s="3" t="n">
-        <v>480</v>
+        <v>1300</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1 кольцо; пара — 990</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N93" s="6" t="n"/>
@@ -5136,45 +5142,49 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>580</v>
+        <v>1490</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>690</v>
+        <v>1850</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.1896551724137931</v>
-      </c>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
+        <v>0.2416107382550337</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>596</v>
+      </c>
       <c r="K94" s="3" t="n">
-        <v>480</v>
+        <v>1300</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1 кольцо; пара — 990</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N94" s="6" t="n"/>
@@ -5182,49 +5192,45 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>2540</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>2540</v>
+        <v>1490</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>853</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>853</v>
-      </c>
+        <v>-0.09395973154362414</v>
+      </c>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="n">
-        <v>1780</v>
+        <v>940</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N95" s="6" t="n"/>
@@ -5232,49 +5238,49 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>979</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>979</v>
+        <v>1490</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>1850</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0</v>
+        <v>0.2416107382550337</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>215</v>
+        <v>596</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>690</v>
+        <v>1300</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +15%; ходовой (45 продаж) — не больше +10%; рост меньше 3% — не трогаю</t>
+          <t>тот же товар, что 0сц</t>
         </is>
       </c>
       <c r="N96" s="6" t="n"/>
@@ -5282,49 +5288,49 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>979</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>979</v>
+        <v>1490</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>1850</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0</v>
+        <v>0.2416107382550337</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>220</v>
+        <v>430</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>220</v>
+        <v>596</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>690</v>
+        <v>1300</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.95): запас до конкурентов</t>
+          <t>тот же товар, что 0сц</t>
         </is>
       </c>
       <c r="N97" s="6" t="n"/>
@@ -5332,49 +5338,49 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1479</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>1479</v>
+        <v>1490</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0</v>
+        <v>-0.09395973154362414</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>395</v>
+        <v>236</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SUPER</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>индекс зелёный (0.89): запас до конкурентов; рост меньше 3% — не трогаю</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N98" s="6" t="n"/>
@@ -5382,49 +5388,49 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1479</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>1479</v>
+        <v>1490</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0</v>
+        <v>-0.09395973154362414</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N99" s="6" t="n"/>
@@ -5432,40 +5438,40 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>979</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>979</v>
+        <v>1490</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0</v>
+        <v>-0.09395973154362414</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -5474,7 +5480,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%; рост меньше 3% — не трогаю</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N100" s="6" t="n"/>
@@ -5482,40 +5488,40 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>1690</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>1690</v>
+        <v>1490</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0</v>
+        <v>-0.09395973154362414</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>333</v>
+        <v>236</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>1180</v>
+        <v>940</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -5524,7 +5530,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>подняли сегодня; цену привели к красивой</t>
         </is>
       </c>
       <c r="N101" s="6" t="n"/>
@@ -5532,40 +5538,40 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>979</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>979</v>
+        <v>1380</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>1350</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0</v>
+        <v>-0.02173913043478259</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>690</v>
+        <v>940</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -5574,7 +5580,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>конкурентов Ozon не видит: +10%; рост меньше 3% — не трогаю</t>
+          <t>ближайшая красивая цена</t>
         </is>
       </c>
       <c r="N102" s="6" t="n"/>
@@ -5582,49 +5588,49 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>3879</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>3879</v>
+        <v>1290</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>1350</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0</v>
+        <v>0.04651162790697683</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>1133</v>
+        <v>258</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>1133</v>
+        <v>286</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>2720</v>
+        <v>940</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N103" s="6" t="n"/>
@@ -5632,49 +5638,45 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>5879</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>5879</v>
+        <v>580</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>685</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>1653</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>1653</v>
-      </c>
+        <v>0.1810344827586208</v>
+      </c>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
       <c r="K104" s="3" t="n">
-        <v>4120</v>
+        <v>480</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>1 кольцо; пара — 990</t>
         </is>
       </c>
       <c r="N104" s="6" t="n"/>
@@ -5682,49 +5684,45 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>8850</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>8850</v>
+        <v>580</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>685</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>2936</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>2936</v>
-      </c>
+        <v>0.1810344827586208</v>
+      </c>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
       <c r="K105" s="3" t="n">
-        <v>6200</v>
+        <v>480</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>1 кольцо; пара — 990</t>
         </is>
       </c>
       <c r="N105" s="6" t="n"/>
@@ -5732,49 +5730,49 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>990</v>
+        <v>2540</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>990</v>
+        <v>2540</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>220</v>
+        <v>853</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>220</v>
+        <v>853</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>690</v>
+        <v>1780</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N106" s="6" t="n"/>
@@ -5782,49 +5780,49 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>6990</v>
+        <v>979</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>6990</v>
+        <v>979</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>1108</v>
+        <v>215</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>1108</v>
+        <v>215</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>4890</v>
+        <v>690</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>конкурентов Ozon не видит: +15%</t>
         </is>
       </c>
       <c r="N107" s="6" t="n"/>
@@ -5832,49 +5830,49 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>3879</v>
+        <v>979</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>3879</v>
+        <v>979</v>
       </c>
       <c r="H108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1299</v>
+        <v>220</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>1299</v>
+        <v>220</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>2720</v>
+        <v>690</v>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>индекс зелёный (0.95): запас до конкурентов</t>
         </is>
       </c>
       <c r="N108" s="6" t="n"/>
@@ -5882,49 +5880,49 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1879</v>
+        <v>1479</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1879</v>
+        <v>1479</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>279</v>
+        <v>395</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>279</v>
+        <v>395</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>1320</v>
+        <v>1040</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>индекс YELLOW: конкуренты дешевле — не поднимаю</t>
+          <t>индекс зелёный (0.89): запас до конкурентов</t>
         </is>
       </c>
       <c r="N109" s="6" t="n"/>
@@ -5932,43 +5930,49 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="3" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>180</v>
+      </c>
       <c r="F110" s="3" t="n">
-        <v>990</v>
+        <v>1479</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>990</v>
+        <v>1479</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="3" t="n"/>
-      <c r="J110" s="3" t="n"/>
+      <c r="I110" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>365</v>
+      </c>
       <c r="K110" s="3" t="n">
-        <v>690</v>
+        <v>1040</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N110" s="6" t="n"/>
@@ -5976,37 +5980,37 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>690</v>
@@ -6018,7 +6022,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N111" s="6" t="n"/>
@@ -6026,49 +6030,49 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>7979</v>
+        <v>979</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>7979</v>
+        <v>979</v>
       </c>
       <c r="H112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2519</v>
+        <v>275</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>2519</v>
+        <v>275</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>5590</v>
+        <v>690</v>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N112" s="6" t="n"/>
@@ -6076,43 +6080,49 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D113" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="3" t="n"/>
+      <c r="E113" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="F113" s="3" t="n">
-        <v>5700</v>
+        <v>3879</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>5700</v>
+        <v>3879</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="n"/>
+      <c r="I113" s="3" t="n">
+        <v>1133</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>1133</v>
+      </c>
       <c r="K113" s="3" t="n">
-        <v>3990</v>
+        <v>2720</v>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N113" s="6" t="n"/>
@@ -6120,43 +6130,49 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>900</v>
+      </c>
       <c r="F114" s="3" t="n">
-        <v>3879</v>
+        <v>5879</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>3879</v>
+        <v>5879</v>
       </c>
       <c r="H114" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="n"/>
+      <c r="I114" s="3" t="n">
+        <v>1653</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>1653</v>
+      </c>
       <c r="K114" s="3" t="n">
-        <v>2720</v>
+        <v>4120</v>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N114" s="6" t="n"/>
@@ -6164,49 +6180,49 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>2790</v>
+        <v>8850</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>2790</v>
+        <v>8850</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>476</v>
+        <v>2936</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>476</v>
+        <v>2936</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>1950</v>
+        <v>6200</v>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N115" s="6" t="n"/>
@@ -6214,45 +6230,49 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>2290</v>
+        <v>3879</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>2290</v>
+        <v>3879</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="n"/>
+      <c r="I116" s="3" t="n">
+        <v>1299</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>1299</v>
+      </c>
       <c r="K116" s="3" t="n">
-        <v>1600</v>
+        <v>2720</v>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N116" s="6" t="n"/>
@@ -6260,49 +6280,49 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1690</v>
+        <v>1879</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1690</v>
+        <v>1879</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>426</v>
+        <v>279</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>426</v>
+        <v>279</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>1180</v>
+        <v>1320</v>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс YELLOW: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N117" s="6" t="n"/>
@@ -6310,28 +6330,26 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n">
-        <v>1490</v>
+        <v>990</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1490</v>
+        <v>990</v>
       </c>
       <c r="H118" s="5" t="n">
         <v>0</v>
@@ -6339,7 +6357,7 @@
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
       <c r="K118" s="3" t="n">
-        <v>1040</v>
+        <v>690</v>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
@@ -6348,7 +6366,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
         </is>
       </c>
       <c r="N118" s="6" t="n"/>
@@ -6356,49 +6374,49 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>1490</v>
+        <v>7979</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>1490</v>
+        <v>7979</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>300</v>
+        <v>2519</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>300</v>
+        <v>2519</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>1040</v>
+        <v>5590</v>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс RED: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N119" s="6" t="n"/>
@@ -6406,49 +6424,43 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="3" t="n">
-        <v>250</v>
-      </c>
+      <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n">
-        <v>1490</v>
+        <v>5700</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>1490</v>
+        <v>5700</v>
       </c>
       <c r="H120" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>300</v>
-      </c>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
       <c r="K120" s="3" t="n">
-        <v>1040</v>
+        <v>3990</v>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
         </is>
       </c>
       <c r="N120" s="6" t="n"/>
@@ -6456,49 +6468,43 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="3" t="n">
-        <v>250</v>
-      </c>
+      <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n">
-        <v>1490</v>
+        <v>3879</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>1490</v>
+        <v>3879</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J121" s="3" t="n">
-        <v>300</v>
-      </c>
+      <c r="I121" s="3" t="n"/>
+      <c r="J121" s="3" t="n"/>
       <c r="K121" s="3" t="n">
-        <v>1040</v>
+        <v>2720</v>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>нет тарифов Ozon (нет карточки?) — не трогаю</t>
         </is>
       </c>
       <c r="N121" s="6" t="n"/>
@@ -6506,49 +6512,49 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>1490</v>
+        <v>999</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1490</v>
+        <v>999</v>
       </c>
       <c r="H122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>1040</v>
+        <v>700</v>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT_INDEX</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>уже подняли сегодня</t>
+          <t>индекс YELLOW: конкуренты дешевле — не поднимаю</t>
         </is>
       </c>
       <c r="N122" s="6" t="n"/>
@@ -6556,49 +6562,49 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>175</v>
+        <v>277</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>175</v>
+        <v>277</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>WITHOUT_INDEX</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>индекс YELLOW: конкуренты дешевле — не поднимаю</t>
+          <t>конкурентов Ozon не видит: +10%</t>
         </is>
       </c>
       <c r="N123" s="6" t="n"/>
@@ -6615,7 +6621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -6624,56 +6630,49 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Цена Ozon и WB одна (правило). Авито и сайт = 70% от неё (60% для дорогих от 50 000) — пересчитаются сами.</t>
+          <t>Красивые цены (правило владельца): чуть ниже круглого уровня — 450, 685, 950, 1 350, 1 850, 2 350, 2 850 … 9 850; от 10 000 — …850 (10 850, 11 850, 12 850).</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Зелёный индекс Ozon: цена для покупателя ниже конкурентов. Поднимаем до 95% от уровня конкурентов, но не больше +25%.</t>
+          <t>Зелёный индекс Ozon (конкуренты дороже): поднимаем к уровню конкурентов. Конкурентов не видно: +10–15%. Красный/жёлтый индекс — не трогаем.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Конкурентов Ozon не видит: +10%, или +15% если маржа на Ozon ниже 25%.</t>
+          <t>Ходовые (20+ продаж) и дорогие (от 50 000) — осторожно, около +10%.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Красный/жёлтый индекс — НЕ поднимаем (конкуренты дешевле, упадём в выдаче и в продажах).</t>
+          <t>Наборы с плитой — лесенкой, «ориг» дороже обычного, дубли (-v2) — одна цена.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ходовые (20+ продаж за ~месяц) и дорогие (от 50 000) — не больше +10%: важнее не потерять продажи.</t>
+          <t>Красным отмечены цены, которые немного СНИЖАЮТСЯ, чтобы стать «красивыми» (например, 1 490 → 1 350).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Цены округлены вниз до …90. Наборы с плитой выстроены лесенкой; «ориг» на 500 дороже обычного; дубли (-v2) — одна цена.</t>
+          <t>Прибыль — с 1 шт на Ozon по тарифам (комиссия 47%), с налогом 6%. Авито и сайт = 70% от цены (пересчитаются сами).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Прибыль — с 1 шт на Ozon по тарифам (комиссия 47%), с налогом 6%. Продажи — заказы с середины сентября (Ozon, WB, Маркет).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Ничего не отправлено. Отметьте в последней колонке, с чем не согласны, и пришлите файл или напишите «да».</t>
+          <t>Ничего не отправлено. Напишите «да» или отметьте в последней колонке, с чем не согласны.</t>
         </is>
       </c>
     </row>
